--- a/dist/Datas/Export Inscription FaceToFace pour admin Formateur1759398900.xlsx
+++ b/dist/Datas/Export Inscription FaceToFace pour admin Formateur1759398900.xlsx
@@ -1,21 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tmhe-my.sharepoint.com/personal/christophe_desandiego_fr_toyota-industries_eu/Documents/Dokument/00-Documents_AE/Documents A_E/00-Dev/Generator/Datas/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_27B727A73FBAC76FBB7D8B2F002CAB68A0620EA6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE624EE5-FA8B-4E8E-BEB6-2E88BDB9B053}"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="29580" yWindow="780" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Export Inscription FaceToFace p" sheetId="1" r:id="rId4"/>
+    <sheet name="Export Inscription FaceToFace p" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Export Inscription FaceToFace p'!$A$1:$Q$624</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1842">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10608" uniqueCount="1842">
   <si>
     <t>userid</t>
   </si>
@@ -5546,14 +5554,9 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -5568,24 +5571,34 @@
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="49" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -5875,14 +5888,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q624"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="8" max="8" width="43.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5935,7 +5948,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
@@ -5988,7 +6001,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>33</v>
       </c>
@@ -6041,7 +6054,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>37</v>
       </c>
@@ -6094,7 +6107,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>41</v>
       </c>
@@ -6147,7 +6160,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>45</v>
       </c>
@@ -6200,7 +6213,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>49</v>
       </c>
@@ -6253,7 +6266,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>63</v>
       </c>
@@ -6306,7 +6319,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>68</v>
       </c>
@@ -6359,7 +6372,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>72</v>
       </c>
@@ -6412,7 +6425,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>76</v>
       </c>
@@ -6465,7 +6478,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>80</v>
       </c>
@@ -6518,7 +6531,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>89</v>
       </c>
@@ -6571,7 +6584,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>93</v>
       </c>
@@ -6624,7 +6637,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>97</v>
       </c>
@@ -6677,7 +6690,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>101</v>
       </c>
@@ -6730,7 +6743,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:17">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>105</v>
       </c>
@@ -6783,7 +6796,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:17">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>108</v>
       </c>
@@ -6836,7 +6849,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:17">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>115</v>
       </c>
@@ -6889,7 +6902,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:17">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>119</v>
       </c>
@@ -6942,7 +6955,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="1:17">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>123</v>
       </c>
@@ -6995,7 +7008,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:17">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>127</v>
       </c>
@@ -7048,7 +7061,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:17">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>131</v>
       </c>
@@ -7101,7 +7114,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:17">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>135</v>
       </c>
@@ -7154,7 +7167,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="1:17">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>142</v>
       </c>
@@ -7207,7 +7220,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="1:17">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>146</v>
       </c>
@@ -7260,7 +7273,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="1:17">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>150</v>
       </c>
@@ -7313,7 +7326,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="28" spans="1:17">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>154</v>
       </c>
@@ -7366,7 +7379,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:17">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>158</v>
       </c>
@@ -7419,7 +7432,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:17">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>162</v>
       </c>
@@ -7472,7 +7485,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="31" spans="1:17">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>176</v>
       </c>
@@ -7525,7 +7538,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="32" spans="1:17">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>180</v>
       </c>
@@ -7578,7 +7591,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="33" spans="1:17">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>183</v>
       </c>
@@ -7631,7 +7644,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="34" spans="1:17">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>187</v>
       </c>
@@ -7684,7 +7697,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="35" spans="1:17">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>192</v>
       </c>
@@ -7737,7 +7750,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="36" spans="1:17">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>196</v>
       </c>
@@ -7790,7 +7803,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="37" spans="1:17">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>203</v>
       </c>
@@ -7843,7 +7856,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="38" spans="1:17">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>207</v>
       </c>
@@ -7896,7 +7909,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="39" spans="1:17">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>211</v>
       </c>
@@ -7949,7 +7962,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="40" spans="1:17">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>214</v>
       </c>
@@ -8002,7 +8015,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="41" spans="1:17">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>158</v>
       </c>
@@ -8055,7 +8068,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="42" spans="1:17">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>226</v>
       </c>
@@ -8108,7 +8121,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="43" spans="1:17">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>230</v>
       </c>
@@ -8161,7 +8174,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="44" spans="1:17">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>233</v>
       </c>
@@ -8214,7 +8227,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="45" spans="1:17">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>237</v>
       </c>
@@ -8267,7 +8280,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="46" spans="1:17">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>241</v>
       </c>
@@ -8320,7 +8333,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="47" spans="1:17">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>252</v>
       </c>
@@ -8373,7 +8386,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="48" spans="1:17">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>257</v>
       </c>
@@ -8426,7 +8439,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="49" spans="1:17">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>260</v>
       </c>
@@ -8479,7 +8492,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="50" spans="1:17">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>266</v>
       </c>
@@ -8532,7 +8545,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="51" spans="1:17">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>270</v>
       </c>
@@ -8585,7 +8598,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="52" spans="1:17">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>274</v>
       </c>
@@ -8638,7 +8651,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="53" spans="1:17">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>278</v>
       </c>
@@ -8691,7 +8704,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="54" spans="1:17">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>282</v>
       </c>
@@ -8744,7 +8757,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="55" spans="1:17">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>288</v>
       </c>
@@ -8797,7 +8810,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="56" spans="1:17">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>292</v>
       </c>
@@ -8850,7 +8863,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="57" spans="1:17">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>296</v>
       </c>
@@ -8903,7 +8916,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="58" spans="1:17">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>300</v>
       </c>
@@ -8956,7 +8969,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="59" spans="1:17">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>304</v>
       </c>
@@ -9009,7 +9022,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="60" spans="1:17">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>308</v>
       </c>
@@ -9062,7 +9075,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="61" spans="1:17">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>316</v>
       </c>
@@ -9115,7 +9128,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="62" spans="1:17">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>319</v>
       </c>
@@ -9168,7 +9181,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="63" spans="1:17">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>323</v>
       </c>
@@ -9221,7 +9234,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="64" spans="1:17">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>326</v>
       </c>
@@ -9274,7 +9287,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="65" spans="1:17">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>330</v>
       </c>
@@ -9327,7 +9340,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="66" spans="1:17">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>334</v>
       </c>
@@ -9380,7 +9393,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="67" spans="1:17">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>337</v>
       </c>
@@ -9433,7 +9446,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="68" spans="1:17">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>341</v>
       </c>
@@ -9486,7 +9499,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="69" spans="1:17">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>345</v>
       </c>
@@ -9539,7 +9552,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="70" spans="1:17">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>348</v>
       </c>
@@ -9592,7 +9605,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="71" spans="1:17">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>351</v>
       </c>
@@ -9645,7 +9658,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="72" spans="1:17">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>357</v>
       </c>
@@ -9698,7 +9711,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="73" spans="1:17">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>362</v>
       </c>
@@ -9751,7 +9764,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="74" spans="1:17">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>365</v>
       </c>
@@ -9804,7 +9817,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="75" spans="1:17">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>368</v>
       </c>
@@ -9857,7 +9870,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="76" spans="1:17">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>158</v>
       </c>
@@ -9910,7 +9923,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="77" spans="1:17">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>380</v>
       </c>
@@ -9963,7 +9976,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="78" spans="1:17">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>105</v>
       </c>
@@ -10016,7 +10029,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="79" spans="1:17">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>101</v>
       </c>
@@ -10069,7 +10082,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="80" spans="1:17">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>383</v>
       </c>
@@ -10122,7 +10135,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="81" spans="1:17">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>387</v>
       </c>
@@ -10175,7 +10188,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="82" spans="1:17">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>391</v>
       </c>
@@ -10228,7 +10241,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="83" spans="1:17">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>398</v>
       </c>
@@ -10281,7 +10294,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="84" spans="1:17">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>402</v>
       </c>
@@ -10334,7 +10347,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="85" spans="1:17">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>406</v>
       </c>
@@ -10387,7 +10400,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="86" spans="1:17">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>410</v>
       </c>
@@ -10440,7 +10453,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="87" spans="1:17">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>414</v>
       </c>
@@ -10493,7 +10506,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="88" spans="1:17">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>192</v>
       </c>
@@ -10546,7 +10559,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="89" spans="1:17">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>426</v>
       </c>
@@ -10599,7 +10612,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="90" spans="1:17">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>430</v>
       </c>
@@ -10652,7 +10665,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="91" spans="1:17">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>434</v>
       </c>
@@ -10705,7 +10718,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="92" spans="1:17">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>131</v>
       </c>
@@ -10758,7 +10771,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="93" spans="1:17">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>49</v>
       </c>
@@ -10811,7 +10824,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="94" spans="1:17">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>142</v>
       </c>
@@ -10864,7 +10877,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="95" spans="1:17">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>97</v>
       </c>
@@ -10917,7 +10930,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="96" spans="1:17">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>237</v>
       </c>
@@ -10970,7 +10983,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="97" spans="1:17">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>440</v>
       </c>
@@ -11023,7 +11036,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="98" spans="1:17">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>443</v>
       </c>
@@ -11076,7 +11089,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="99" spans="1:17">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>447</v>
       </c>
@@ -11129,7 +11142,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="100" spans="1:17">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>454</v>
       </c>
@@ -11182,7 +11195,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="101" spans="1:17">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>457</v>
       </c>
@@ -11235,7 +11248,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="102" spans="1:17">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>461</v>
       </c>
@@ -11288,7 +11301,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="103" spans="1:17">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>464</v>
       </c>
@@ -11341,7 +11354,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="104" spans="1:17">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>468</v>
       </c>
@@ -11394,7 +11407,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="105" spans="1:17">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>472</v>
       </c>
@@ -11447,7 +11460,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="106" spans="1:17">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>479</v>
       </c>
@@ -11500,7 +11513,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="107" spans="1:17">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>483</v>
       </c>
@@ -11553,7 +11566,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="108" spans="1:17">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>487</v>
       </c>
@@ -11606,7 +11619,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="109" spans="1:17">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>490</v>
       </c>
@@ -11659,7 +11672,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="110" spans="1:17">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>494</v>
       </c>
@@ -11712,7 +11725,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="111" spans="1:17">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>497</v>
       </c>
@@ -11765,7 +11778,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="112" spans="1:17">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>501</v>
       </c>
@@ -11818,7 +11831,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="113" spans="1:17">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>513</v>
       </c>
@@ -11871,7 +11884,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="114" spans="1:17">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>518</v>
       </c>
@@ -11924,7 +11937,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="115" spans="1:17">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>522</v>
       </c>
@@ -11977,7 +11990,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="116" spans="1:17">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>531</v>
       </c>
@@ -12030,7 +12043,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="117" spans="1:17">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>357</v>
       </c>
@@ -12083,7 +12096,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="118" spans="1:17">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>535</v>
       </c>
@@ -12136,7 +12149,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="119" spans="1:17">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>540</v>
       </c>
@@ -12189,7 +12202,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="120" spans="1:17">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>543</v>
       </c>
@@ -12242,7 +12255,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="121" spans="1:17">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>554</v>
       </c>
@@ -12295,7 +12308,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="122" spans="1:17">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>558</v>
       </c>
@@ -12348,7 +12361,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="123" spans="1:17">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>561</v>
       </c>
@@ -12401,7 +12414,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="124" spans="1:17">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>573</v>
       </c>
@@ -12454,7 +12467,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="125" spans="1:17">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>288</v>
       </c>
@@ -12507,7 +12520,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="126" spans="1:17">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>576</v>
       </c>
@@ -12560,7 +12573,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="127" spans="1:17">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>580</v>
       </c>
@@ -12613,7 +12626,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="128" spans="1:17">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>316</v>
       </c>
@@ -12666,7 +12679,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="129" spans="1:17">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>583</v>
       </c>
@@ -12719,7 +12732,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="130" spans="1:17">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>63</v>
       </c>
@@ -12772,7 +12785,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="131" spans="1:17">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>72</v>
       </c>
@@ -12825,7 +12838,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="132" spans="1:17">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>590</v>
       </c>
@@ -12878,7 +12891,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="133" spans="1:17">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>593</v>
       </c>
@@ -12931,7 +12944,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="134" spans="1:17">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>296</v>
       </c>
@@ -12984,7 +12997,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="135" spans="1:17">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>278</v>
       </c>
@@ -13037,7 +13050,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="136" spans="1:17">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>300</v>
       </c>
@@ -13090,7 +13103,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="137" spans="1:17">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>598</v>
       </c>
@@ -13143,7 +13156,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="138" spans="1:17">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>602</v>
       </c>
@@ -13196,7 +13209,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="139" spans="1:17">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>606</v>
       </c>
@@ -13249,7 +13262,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="140" spans="1:17">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>609</v>
       </c>
@@ -13302,7 +13315,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="141" spans="1:17">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>615</v>
       </c>
@@ -13355,7 +13368,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="142" spans="1:17">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>618</v>
       </c>
@@ -13408,7 +13421,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="143" spans="1:17">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>622</v>
       </c>
@@ -13461,7 +13474,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="144" spans="1:17">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>625</v>
       </c>
@@ -13514,7 +13527,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="145" spans="1:17">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>629</v>
       </c>
@@ -13567,7 +13580,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="146" spans="1:17">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>49</v>
       </c>
@@ -13620,7 +13633,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="147" spans="1:17">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>443</v>
       </c>
@@ -13673,7 +13686,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="148" spans="1:17">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>636</v>
       </c>
@@ -13726,7 +13739,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="149" spans="1:17">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>639</v>
       </c>
@@ -13779,7 +13792,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="150" spans="1:17">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>642</v>
       </c>
@@ -13832,7 +13845,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="151" spans="1:17">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>645</v>
       </c>
@@ -13885,7 +13898,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="152" spans="1:17">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>410</v>
       </c>
@@ -13938,7 +13951,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="153" spans="1:17">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>654</v>
       </c>
@@ -13991,7 +14004,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="154" spans="1:17">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>326</v>
       </c>
@@ -14044,7 +14057,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="155" spans="1:17">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>658</v>
       </c>
@@ -14097,7 +14110,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="156" spans="1:17">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>661</v>
       </c>
@@ -14150,7 +14163,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="157" spans="1:17">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>664</v>
       </c>
@@ -14203,7 +14216,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="158" spans="1:17">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>668</v>
       </c>
@@ -14256,7 +14269,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="159" spans="1:17">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>674</v>
       </c>
@@ -14309,7 +14322,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="160" spans="1:17">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>678</v>
       </c>
@@ -14362,7 +14375,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="161" spans="1:17">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>681</v>
       </c>
@@ -14415,7 +14428,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="162" spans="1:17">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>684</v>
       </c>
@@ -14468,7 +14481,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="163" spans="1:17">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>615</v>
       </c>
@@ -14521,7 +14534,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="164" spans="1:17">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>625</v>
       </c>
@@ -14574,7 +14587,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="165" spans="1:17">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>695</v>
       </c>
@@ -14627,7 +14640,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="166" spans="1:17">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>698</v>
       </c>
@@ -14680,7 +14693,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="167" spans="1:17">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>461</v>
       </c>
@@ -14733,7 +14746,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="168" spans="1:17">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>192</v>
       </c>
@@ -14786,7 +14799,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="169" spans="1:17">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>622</v>
       </c>
@@ -14839,7 +14852,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="170" spans="1:17">
+    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>704</v>
       </c>
@@ -14892,7 +14905,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="171" spans="1:17">
+    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>707</v>
       </c>
@@ -14945,7 +14958,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="172" spans="1:17">
+    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>710</v>
       </c>
@@ -14998,7 +15011,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="173" spans="1:17">
+    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>678</v>
       </c>
@@ -15051,7 +15064,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="174" spans="1:17">
+    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>713</v>
       </c>
@@ -15104,7 +15117,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="175" spans="1:17">
+    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>192</v>
       </c>
@@ -15157,7 +15170,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="176" spans="1:17">
+    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>430</v>
       </c>
@@ -15210,7 +15223,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="177" spans="1:17">
+    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>426</v>
       </c>
@@ -15263,7 +15276,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="178" spans="1:17">
+    <row r="178" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>721</v>
       </c>
@@ -15316,7 +15329,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="179" spans="1:17">
+    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>725</v>
       </c>
@@ -15369,7 +15382,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="180" spans="1:17">
+    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>729</v>
       </c>
@@ -15422,7 +15435,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="181" spans="1:17">
+    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>127</v>
       </c>
@@ -15475,7 +15488,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="182" spans="1:17">
+    <row r="182" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>668</v>
       </c>
@@ -15528,7 +15541,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="183" spans="1:17">
+    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>739</v>
       </c>
@@ -15581,7 +15594,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="184" spans="1:17">
+    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>742</v>
       </c>
@@ -15634,7 +15647,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="185" spans="1:17">
+    <row r="185" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>746</v>
       </c>
@@ -15687,7 +15700,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="186" spans="1:17">
+    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>749</v>
       </c>
@@ -15740,7 +15753,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="187" spans="1:17">
+    <row r="187" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>63</v>
       </c>
@@ -15793,7 +15806,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="188" spans="1:17">
+    <row r="188" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>531</v>
       </c>
@@ -15846,7 +15859,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="189" spans="1:17">
+    <row r="189" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>761</v>
       </c>
@@ -15899,7 +15912,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="190" spans="1:17">
+    <row r="190" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>765</v>
       </c>
@@ -15952,7 +15965,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="191" spans="1:17">
+    <row r="191" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>180</v>
       </c>
@@ -16005,7 +16018,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="192" spans="1:17">
+    <row r="192" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>771</v>
       </c>
@@ -16058,7 +16071,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="193" spans="1:17">
+    <row r="193" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>483</v>
       </c>
@@ -16111,7 +16124,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="194" spans="1:17">
+    <row r="194" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>494</v>
       </c>
@@ -16164,7 +16177,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="195" spans="1:17">
+    <row r="195" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>775</v>
       </c>
@@ -16217,7 +16230,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="196" spans="1:17">
+    <row r="196" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>779</v>
       </c>
@@ -16270,7 +16283,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="197" spans="1:17">
+    <row r="197" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>196</v>
       </c>
@@ -16323,7 +16336,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="198" spans="1:17">
+    <row r="198" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>786</v>
       </c>
@@ -16376,7 +16389,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="199" spans="1:17">
+    <row r="199" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>203</v>
       </c>
@@ -16429,7 +16442,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="200" spans="1:17">
+    <row r="200" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>761</v>
       </c>
@@ -16482,7 +16495,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="201" spans="1:17">
+    <row r="201" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>790</v>
       </c>
@@ -16535,7 +16548,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="202" spans="1:17">
+    <row r="202" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>793</v>
       </c>
@@ -16588,7 +16601,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="203" spans="1:17">
+    <row r="203" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>800</v>
       </c>
@@ -16641,7 +16654,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="204" spans="1:17">
+    <row r="204" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>803</v>
       </c>
@@ -16694,7 +16707,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="205" spans="1:17">
+    <row r="205" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>590</v>
       </c>
@@ -16747,7 +16760,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="206" spans="1:17">
+    <row r="206" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>806</v>
       </c>
@@ -16800,7 +16813,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="207" spans="1:17">
+    <row r="207" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>654</v>
       </c>
@@ -16853,7 +16866,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="208" spans="1:17">
+    <row r="208" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>809</v>
       </c>
@@ -16906,7 +16919,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="209" spans="1:17">
+    <row r="209" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>820</v>
       </c>
@@ -16959,7 +16972,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="210" spans="1:17">
+    <row r="210" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>824</v>
       </c>
@@ -17012,7 +17025,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="211" spans="1:17">
+    <row r="211" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>63</v>
       </c>
@@ -17065,7 +17078,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="212" spans="1:17">
+    <row r="212" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>828</v>
       </c>
@@ -17118,7 +17131,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="213" spans="1:17">
+    <row r="213" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>831</v>
       </c>
@@ -17171,7 +17184,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="214" spans="1:17">
+    <row r="214" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>775</v>
       </c>
@@ -17224,7 +17237,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="215" spans="1:17">
+    <row r="215" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>839</v>
       </c>
@@ -17277,7 +17290,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="216" spans="1:17">
+    <row r="216" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>842</v>
       </c>
@@ -17330,7 +17343,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="217" spans="1:17">
+    <row r="217" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>846</v>
       </c>
@@ -17383,7 +17396,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="218" spans="1:17">
+    <row r="218" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>849</v>
       </c>
@@ -17436,7 +17449,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="219" spans="1:17">
+    <row r="219" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>852</v>
       </c>
@@ -17489,7 +17502,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="220" spans="1:17">
+    <row r="220" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>472</v>
       </c>
@@ -17542,7 +17555,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="221" spans="1:17">
+    <row r="221" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>410</v>
       </c>
@@ -17595,7 +17608,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="222" spans="1:17">
+    <row r="222" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>326</v>
       </c>
@@ -17648,7 +17661,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="223" spans="1:17">
+    <row r="223" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>319</v>
       </c>
@@ -17701,7 +17714,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="224" spans="1:17">
+    <row r="224" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>859</v>
       </c>
@@ -17754,7 +17767,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="225" spans="1:17">
+    <row r="225" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>862</v>
       </c>
@@ -17807,7 +17820,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="226" spans="1:17">
+    <row r="226" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
         <v>868</v>
       </c>
@@ -17860,7 +17873,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="227" spans="1:17">
+    <row r="227" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
         <v>872</v>
       </c>
@@ -17913,7 +17926,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="228" spans="1:17">
+    <row r="228" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>876</v>
       </c>
@@ -17966,7 +17979,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="229" spans="1:17">
+    <row r="229" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
         <v>880</v>
       </c>
@@ -18019,7 +18032,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="230" spans="1:17">
+    <row r="230" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
         <v>884</v>
       </c>
@@ -18072,7 +18085,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="231" spans="1:17">
+    <row r="231" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>654</v>
       </c>
@@ -18125,7 +18138,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="232" spans="1:17">
+    <row r="232" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>593</v>
       </c>
@@ -18178,7 +18191,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="233" spans="1:17">
+    <row r="233" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>890</v>
       </c>
@@ -18231,7 +18244,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="234" spans="1:17">
+    <row r="234" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>274</v>
       </c>
@@ -18284,7 +18297,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="235" spans="1:17">
+    <row r="235" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>894</v>
       </c>
@@ -18337,7 +18350,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="236" spans="1:17">
+    <row r="236" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>901</v>
       </c>
@@ -18390,7 +18403,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="237" spans="1:17">
+    <row r="237" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>192</v>
       </c>
@@ -18443,7 +18456,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="238" spans="1:17">
+    <row r="238" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
         <v>905</v>
       </c>
@@ -18496,7 +18509,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="239" spans="1:17">
+    <row r="239" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
         <v>282</v>
       </c>
@@ -18549,7 +18562,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="240" spans="1:17">
+    <row r="240" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
         <v>908</v>
       </c>
@@ -18602,7 +18615,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="241" spans="1:17">
+    <row r="241" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>316</v>
       </c>
@@ -18655,7 +18668,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="242" spans="1:17">
+    <row r="242" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
         <v>196</v>
       </c>
@@ -18708,7 +18721,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="243" spans="1:17">
+    <row r="243" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
         <v>203</v>
       </c>
@@ -18761,7 +18774,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="244" spans="1:17">
+    <row r="244" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
         <v>914</v>
       </c>
@@ -18814,7 +18827,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="245" spans="1:17">
+    <row r="245" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
         <v>658</v>
       </c>
@@ -18867,7 +18880,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="246" spans="1:17">
+    <row r="246" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
         <v>917</v>
       </c>
@@ -18920,7 +18933,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="247" spans="1:17">
+    <row r="247" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
         <v>924</v>
       </c>
@@ -18973,7 +18986,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="248" spans="1:17">
+    <row r="248" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
         <v>928</v>
       </c>
@@ -19026,7 +19039,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="249" spans="1:17">
+    <row r="249" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
         <v>931</v>
       </c>
@@ -19079,7 +19092,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="250" spans="1:17">
+    <row r="250" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
         <v>606</v>
       </c>
@@ -19132,7 +19145,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="251" spans="1:17">
+    <row r="251" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
         <v>154</v>
       </c>
@@ -19185,7 +19198,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="252" spans="1:17">
+    <row r="252" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
         <v>934</v>
       </c>
@@ -19238,7 +19251,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="253" spans="1:17">
+    <row r="253" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
         <v>941</v>
       </c>
@@ -19291,7 +19304,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="254" spans="1:17">
+    <row r="254" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
         <v>440</v>
       </c>
@@ -19344,7 +19357,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="255" spans="1:17">
+    <row r="255" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
         <v>945</v>
       </c>
@@ -19397,7 +19410,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="256" spans="1:17">
+    <row r="256" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
         <v>948</v>
       </c>
@@ -19450,7 +19463,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="257" spans="1:17">
+    <row r="257" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
         <v>951</v>
       </c>
@@ -19503,7 +19516,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="258" spans="1:17">
+    <row r="258" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>398</v>
       </c>
@@ -19556,7 +19569,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="259" spans="1:17">
+    <row r="259" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
         <v>960</v>
       </c>
@@ -19609,7 +19622,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="260" spans="1:17">
+    <row r="260" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>963</v>
       </c>
@@ -19662,7 +19675,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="261" spans="1:17">
+    <row r="261" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
         <v>924</v>
       </c>
@@ -19715,7 +19728,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="262" spans="1:17">
+    <row r="262" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
         <v>969</v>
       </c>
@@ -19768,7 +19781,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="263" spans="1:17">
+    <row r="263" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
         <v>974</v>
       </c>
@@ -19821,7 +19834,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="264" spans="1:17">
+    <row r="264" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
         <v>977</v>
       </c>
@@ -19874,7 +19887,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="265" spans="1:17">
+    <row r="265" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
         <v>981</v>
       </c>
@@ -19927,7 +19940,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="266" spans="1:17">
+    <row r="266" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
         <v>928</v>
       </c>
@@ -19980,7 +19993,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="267" spans="1:17">
+    <row r="267" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
         <v>713</v>
       </c>
@@ -20033,7 +20046,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="268" spans="1:17">
+    <row r="268" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
         <v>987</v>
       </c>
@@ -20086,7 +20099,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="269" spans="1:17">
+    <row r="269" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
         <v>183</v>
       </c>
@@ -20139,7 +20152,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="270" spans="1:17">
+    <row r="270" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
         <v>990</v>
       </c>
@@ -20192,7 +20205,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="271" spans="1:17">
+    <row r="271" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
         <v>993</v>
       </c>
@@ -20245,7 +20258,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="272" spans="1:17">
+    <row r="272" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
         <v>996</v>
       </c>
@@ -20298,7 +20311,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="273" spans="1:17">
+    <row r="273" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
         <v>803</v>
       </c>
@@ -20351,7 +20364,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="274" spans="1:17">
+    <row r="274" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
         <v>1003</v>
       </c>
@@ -20404,7 +20417,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="275" spans="1:17">
+    <row r="275" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
         <v>1007</v>
       </c>
@@ -20457,7 +20470,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="276" spans="1:17">
+    <row r="276" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
         <v>1010</v>
       </c>
@@ -20510,7 +20523,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="277" spans="1:17">
+    <row r="277" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
         <v>1015</v>
       </c>
@@ -20563,7 +20576,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="278" spans="1:17">
+    <row r="278" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
         <v>1017</v>
       </c>
@@ -20616,7 +20629,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="279" spans="1:17">
+    <row r="279" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
         <v>1020</v>
       </c>
@@ -20669,7 +20682,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="280" spans="1:17">
+    <row r="280" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
         <v>1023</v>
       </c>
@@ -20722,7 +20735,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="281" spans="1:17">
+    <row r="281" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
         <v>1027</v>
       </c>
@@ -20775,7 +20788,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="282" spans="1:17">
+    <row r="282" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
         <v>1031</v>
       </c>
@@ -20828,7 +20841,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="283" spans="1:17">
+    <row r="283" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
         <v>142</v>
       </c>
@@ -20881,7 +20894,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="284" spans="1:17">
+    <row r="284" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
         <v>1039</v>
       </c>
@@ -20934,7 +20947,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="285" spans="1:17">
+    <row r="285" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
         <v>1043</v>
       </c>
@@ -20987,7 +21000,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="286" spans="1:17">
+    <row r="286" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
         <v>593</v>
       </c>
@@ -21040,7 +21053,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="287" spans="1:17">
+    <row r="287" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
         <v>1050</v>
       </c>
@@ -21093,7 +21106,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="288" spans="1:17">
+    <row r="288" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
         <v>1055</v>
       </c>
@@ -21146,7 +21159,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="289" spans="1:17">
+    <row r="289" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
         <v>1058</v>
       </c>
@@ -21199,7 +21212,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="290" spans="1:17">
+    <row r="290" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
         <v>1062</v>
       </c>
@@ -21252,7 +21265,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="291" spans="1:17">
+    <row r="291" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
         <v>1065</v>
       </c>
@@ -21305,7 +21318,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="292" spans="1:17">
+    <row r="292" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
         <v>642</v>
       </c>
@@ -21358,7 +21371,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="293" spans="1:17">
+    <row r="293" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
         <v>1071</v>
       </c>
@@ -21411,7 +21424,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="294" spans="1:17">
+    <row r="294" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
         <v>928</v>
       </c>
@@ -21464,7 +21477,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="295" spans="1:17">
+    <row r="295" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
         <v>1074</v>
       </c>
@@ -21517,7 +21530,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="296" spans="1:17">
+    <row r="296" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
         <v>698</v>
       </c>
@@ -21570,7 +21583,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="297" spans="1:17">
+    <row r="297" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
         <v>576</v>
       </c>
@@ -21623,7 +21636,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="298" spans="1:17">
+    <row r="298" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
         <v>831</v>
       </c>
@@ -21676,7 +21689,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="299" spans="1:17">
+    <row r="299" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
         <v>1080</v>
       </c>
@@ -21729,7 +21742,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="300" spans="1:17">
+    <row r="300" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
         <v>1084</v>
       </c>
@@ -21782,7 +21795,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="301" spans="1:17">
+    <row r="301" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
         <v>430</v>
       </c>
@@ -21835,7 +21848,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="302" spans="1:17">
+    <row r="302" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
         <v>1087</v>
       </c>
@@ -21888,7 +21901,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="303" spans="1:17">
+    <row r="303" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
         <v>1091</v>
       </c>
@@ -21941,7 +21954,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="304" spans="1:17">
+    <row r="304" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
         <v>645</v>
       </c>
@@ -21994,7 +22007,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="305" spans="1:17">
+    <row r="305" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
         <v>1099</v>
       </c>
@@ -22047,7 +22060,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="306" spans="1:17">
+    <row r="306" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
         <v>981</v>
       </c>
@@ -22100,7 +22113,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="307" spans="1:17">
+    <row r="307" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
         <v>443</v>
       </c>
@@ -22153,7 +22166,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="308" spans="1:17">
+    <row r="308" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
         <v>917</v>
       </c>
@@ -22206,7 +22219,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="309" spans="1:17">
+    <row r="309" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
         <v>1043</v>
       </c>
@@ -22259,7 +22272,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="310" spans="1:17">
+    <row r="310" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
         <v>661</v>
       </c>
@@ -22312,7 +22325,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="311" spans="1:17">
+    <row r="311" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
         <v>1104</v>
       </c>
@@ -22365,7 +22378,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="312" spans="1:17">
+    <row r="312" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
         <v>1107</v>
       </c>
@@ -22418,7 +22431,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="313" spans="1:17">
+    <row r="313" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
         <v>1110</v>
       </c>
@@ -22471,7 +22484,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="314" spans="1:17">
+    <row r="314" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
         <v>316</v>
       </c>
@@ -22524,7 +22537,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="315" spans="1:17">
+    <row r="315" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
         <v>761</v>
       </c>
@@ -22577,7 +22590,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="316" spans="1:17">
+    <row r="316" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
         <v>786</v>
       </c>
@@ -22630,7 +22643,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="317" spans="1:17">
+    <row r="317" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
         <v>969</v>
       </c>
@@ -22683,7 +22696,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="318" spans="1:17">
+    <row r="318" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
         <v>1115</v>
       </c>
@@ -22736,7 +22749,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="319" spans="1:17">
+    <row r="319" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
         <v>531</v>
       </c>
@@ -22789,7 +22802,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="320" spans="1:17">
+    <row r="320" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
         <v>806</v>
       </c>
@@ -22842,7 +22855,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="321" spans="1:17">
+    <row r="321" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
         <v>1126</v>
       </c>
@@ -22895,7 +22908,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="322" spans="1:17">
+    <row r="322" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
         <v>49</v>
       </c>
@@ -22948,7 +22961,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="323" spans="1:17">
+    <row r="323" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
         <v>771</v>
       </c>
@@ -23001,7 +23014,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="324" spans="1:17">
+    <row r="324" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
         <v>1133</v>
       </c>
@@ -23054,7 +23067,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="325" spans="1:17">
+    <row r="325" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
         <v>1136</v>
       </c>
@@ -23107,7 +23120,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="326" spans="1:17">
+    <row r="326" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
         <v>1139</v>
       </c>
@@ -23160,7 +23173,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="327" spans="1:17">
+    <row r="327" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
         <v>1142</v>
       </c>
@@ -23213,7 +23226,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="328" spans="1:17">
+    <row r="328" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
         <v>497</v>
       </c>
@@ -23266,7 +23279,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="329" spans="1:17">
+    <row r="329" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
         <v>1147</v>
       </c>
@@ -23319,7 +23332,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="330" spans="1:17">
+    <row r="330" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
         <v>859</v>
       </c>
@@ -23372,7 +23385,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="331" spans="1:17">
+    <row r="331" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
         <v>1104</v>
       </c>
@@ -23425,7 +23438,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="332" spans="1:17">
+    <row r="332" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
         <v>1151</v>
       </c>
@@ -23478,7 +23491,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="333" spans="1:17">
+    <row r="333" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
         <v>1158</v>
       </c>
@@ -23531,7 +23544,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="334" spans="1:17">
+    <row r="334" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
         <v>41</v>
       </c>
@@ -23584,7 +23597,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="335" spans="1:17">
+    <row r="335" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
         <v>1161</v>
       </c>
@@ -23637,7 +23650,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="336" spans="1:17">
+    <row r="336" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
         <v>1164</v>
       </c>
@@ -23690,7 +23703,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="337" spans="1:17">
+    <row r="337" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
         <v>345</v>
       </c>
@@ -23743,7 +23756,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="338" spans="1:17">
+    <row r="338" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
         <v>1171</v>
       </c>
@@ -23796,7 +23809,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="339" spans="1:17">
+    <row r="339" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
         <v>1178</v>
       </c>
@@ -23849,7 +23862,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="340" spans="1:17">
+    <row r="340" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
         <v>1181</v>
       </c>
@@ -23902,7 +23915,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="341" spans="1:17">
+    <row r="341" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
         <v>1185</v>
       </c>
@@ -23955,7 +23968,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="342" spans="1:17">
+    <row r="342" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
         <v>1189</v>
       </c>
@@ -24008,7 +24021,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="343" spans="1:17">
+    <row r="343" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
         <v>1192</v>
       </c>
@@ -24061,7 +24074,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="344" spans="1:17">
+    <row r="344" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
         <v>531</v>
       </c>
@@ -24114,7 +24127,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="345" spans="1:17">
+    <row r="345" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
         <v>1198</v>
       </c>
@@ -24167,7 +24180,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="346" spans="1:17">
+    <row r="346" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
         <v>868</v>
       </c>
@@ -24220,7 +24233,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="347" spans="1:17">
+    <row r="347" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
         <v>1205</v>
       </c>
@@ -24273,7 +24286,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="348" spans="1:17">
+    <row r="348" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
         <v>1210</v>
       </c>
@@ -24326,7 +24339,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="349" spans="1:17">
+    <row r="349" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
         <v>742</v>
       </c>
@@ -24379,7 +24392,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="350" spans="1:17">
+    <row r="350" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
         <v>1213</v>
       </c>
@@ -24432,7 +24445,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="351" spans="1:17">
+    <row r="351" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
         <v>1217</v>
       </c>
@@ -24485,7 +24498,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="352" spans="1:17">
+    <row r="352" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
         <v>443</v>
       </c>
@@ -24538,7 +24551,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="353" spans="1:17">
+    <row r="353" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
         <v>1223</v>
       </c>
@@ -24591,7 +24604,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="354" spans="1:17">
+    <row r="354" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
         <v>1226</v>
       </c>
@@ -24644,7 +24657,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="355" spans="1:17">
+    <row r="355" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
         <v>1229</v>
       </c>
@@ -24697,7 +24710,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="356" spans="1:17">
+    <row r="356" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="s">
         <v>1232</v>
       </c>
@@ -24750,7 +24763,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="357" spans="1:17">
+    <row r="357" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="s">
         <v>1237</v>
       </c>
@@ -24803,7 +24816,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="358" spans="1:17">
+    <row r="358" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A358" s="1" t="s">
         <v>540</v>
       </c>
@@ -24856,7 +24869,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="359" spans="1:17">
+    <row r="359" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A359" s="1" t="s">
         <v>72</v>
       </c>
@@ -24909,7 +24922,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="360" spans="1:17">
+    <row r="360" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A360" s="1" t="s">
         <v>1243</v>
       </c>
@@ -24962,7 +24975,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="361" spans="1:17">
+    <row r="361" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A361" s="1" t="s">
         <v>1246</v>
       </c>
@@ -25015,7 +25028,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="362" spans="1:17">
+    <row r="362" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A362" s="1" t="s">
         <v>1249</v>
       </c>
@@ -25068,7 +25081,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="363" spans="1:17">
+    <row r="363" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="s">
         <v>1252</v>
       </c>
@@ -25121,7 +25134,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="364" spans="1:17">
+    <row r="364" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="s">
         <v>1256</v>
       </c>
@@ -25174,7 +25187,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="365" spans="1:17">
+    <row r="365" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A365" s="1" t="s">
         <v>278</v>
       </c>
@@ -25227,7 +25240,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="366" spans="1:17">
+    <row r="366" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A366" s="1" t="s">
         <v>1262</v>
       </c>
@@ -25280,7 +25293,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="367" spans="1:17">
+    <row r="367" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="s">
         <v>1139</v>
       </c>
@@ -25333,7 +25346,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="368" spans="1:17">
+    <row r="368" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A368" s="1" t="s">
         <v>49</v>
       </c>
@@ -25386,7 +25399,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="369" spans="1:17">
+    <row r="369" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="s">
         <v>1266</v>
       </c>
@@ -25439,7 +25452,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="370" spans="1:17">
+    <row r="370" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A370" s="1" t="s">
         <v>1270</v>
       </c>
@@ -25492,7 +25505,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="371" spans="1:17">
+    <row r="371" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A371" s="1" t="s">
         <v>661</v>
       </c>
@@ -25545,7 +25558,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="372" spans="1:17">
+    <row r="372" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
         <v>1273</v>
       </c>
@@ -25598,7 +25611,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="373" spans="1:17">
+    <row r="373" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A373" s="1" t="s">
         <v>1276</v>
       </c>
@@ -25651,7 +25664,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="374" spans="1:17">
+    <row r="374" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A374" s="1" t="s">
         <v>1279</v>
       </c>
@@ -25704,7 +25717,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="375" spans="1:17">
+    <row r="375" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A375" s="1" t="s">
         <v>580</v>
       </c>
@@ -25757,7 +25770,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="376" spans="1:17">
+    <row r="376" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A376" s="1" t="s">
         <v>707</v>
       </c>
@@ -25810,7 +25823,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="377" spans="1:17">
+    <row r="377" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A377" s="1" t="s">
         <v>710</v>
       </c>
@@ -25863,7 +25876,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="378" spans="1:17">
+    <row r="378" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A378" s="1" t="s">
         <v>1286</v>
       </c>
@@ -25916,7 +25929,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="379" spans="1:17">
+    <row r="379" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A379" s="1" t="s">
         <v>288</v>
       </c>
@@ -25969,7 +25982,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="380" spans="1:17">
+    <row r="380" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A380" s="1" t="s">
         <v>1289</v>
       </c>
@@ -26022,7 +26035,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="381" spans="1:17">
+    <row r="381" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A381" s="1" t="s">
         <v>1292</v>
       </c>
@@ -26075,7 +26088,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="382" spans="1:17">
+    <row r="382" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A382" s="1" t="s">
         <v>1298</v>
       </c>
@@ -26128,7 +26141,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="383" spans="1:17">
+    <row r="383" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A383" s="1" t="s">
         <v>1065</v>
       </c>
@@ -26181,7 +26194,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="384" spans="1:17">
+    <row r="384" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A384" s="1" t="s">
         <v>1301</v>
       </c>
@@ -26234,7 +26247,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="385" spans="1:17">
+    <row r="385" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A385" s="1" t="s">
         <v>1305</v>
       </c>
@@ -26287,7 +26300,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="386" spans="1:17">
+    <row r="386" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A386" s="1" t="s">
         <v>1309</v>
       </c>
@@ -26340,7 +26353,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="387" spans="1:17">
+    <row r="387" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A387" s="1" t="s">
         <v>1178</v>
       </c>
@@ -26393,7 +26406,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="388" spans="1:17">
+    <row r="388" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A388" s="1" t="s">
         <v>1315</v>
       </c>
@@ -26446,7 +26459,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="389" spans="1:17">
+    <row r="389" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A389" s="1" t="s">
         <v>1318</v>
       </c>
@@ -26499,7 +26512,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="390" spans="1:17">
+    <row r="390" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A390" s="1" t="s">
         <v>1321</v>
       </c>
@@ -26552,7 +26565,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="391" spans="1:17">
+    <row r="391" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A391" s="1" t="s">
         <v>1324</v>
       </c>
@@ -26605,7 +26618,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="392" spans="1:17">
+    <row r="392" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A392" s="1" t="s">
         <v>1164</v>
       </c>
@@ -26658,7 +26671,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="393" spans="1:17">
+    <row r="393" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A393" s="1" t="s">
         <v>1327</v>
       </c>
@@ -26711,7 +26724,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="394" spans="1:17">
+    <row r="394" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A394" s="1" t="s">
         <v>1334</v>
       </c>
@@ -26764,7 +26777,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="395" spans="1:17">
+    <row r="395" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A395" s="1" t="s">
         <v>934</v>
       </c>
@@ -26817,7 +26830,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="396" spans="1:17">
+    <row r="396" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A396" s="1" t="s">
         <v>1337</v>
       </c>
@@ -26870,7 +26883,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="397" spans="1:17">
+    <row r="397" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A397" s="1" t="s">
         <v>993</v>
       </c>
@@ -26923,7 +26936,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="398" spans="1:17">
+    <row r="398" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A398" s="1" t="s">
         <v>1340</v>
       </c>
@@ -26976,7 +26989,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="399" spans="1:17">
+    <row r="399" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A399" s="1" t="s">
         <v>960</v>
       </c>
@@ -27029,7 +27042,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="400" spans="1:17">
+    <row r="400" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A400" s="1" t="s">
         <v>1347</v>
       </c>
@@ -27082,7 +27095,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="401" spans="1:17">
+    <row r="401" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A401" s="1" t="s">
         <v>1350</v>
       </c>
@@ -27135,7 +27148,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="402" spans="1:17">
+    <row r="402" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A402" s="1" t="s">
         <v>1353</v>
       </c>
@@ -27188,7 +27201,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="403" spans="1:17">
+    <row r="403" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A403" s="1" t="s">
         <v>1356</v>
       </c>
@@ -27241,7 +27254,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="404" spans="1:17">
+    <row r="404" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A404" s="1" t="s">
         <v>1361</v>
       </c>
@@ -27294,7 +27307,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="405" spans="1:17">
+    <row r="405" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A405" s="1" t="s">
         <v>1364</v>
       </c>
@@ -27347,7 +27360,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="406" spans="1:17">
+    <row r="406" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A406" s="1" t="s">
         <v>824</v>
       </c>
@@ -27400,7 +27413,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="407" spans="1:17">
+    <row r="407" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A407" s="1" t="s">
         <v>63</v>
       </c>
@@ -27453,7 +27466,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="408" spans="1:17">
+    <row r="408" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A408" s="1" t="s">
         <v>1370</v>
       </c>
@@ -27506,7 +27519,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="409" spans="1:17">
+    <row r="409" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A409" s="1" t="s">
         <v>908</v>
       </c>
@@ -27559,7 +27572,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="410" spans="1:17">
+    <row r="410" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A410" s="1" t="s">
         <v>1104</v>
       </c>
@@ -27612,7 +27625,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="411" spans="1:17">
+    <row r="411" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A411" s="1" t="s">
         <v>1373</v>
       </c>
@@ -27665,7 +27678,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="412" spans="1:17">
+    <row r="412" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A412" s="1" t="s">
         <v>1380</v>
       </c>
@@ -27718,7 +27731,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="413" spans="1:17">
+    <row r="413" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A413" s="1" t="s">
         <v>37</v>
       </c>
@@ -27771,7 +27784,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="414" spans="1:17">
+    <row r="414" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A414" s="1" t="s">
         <v>1384</v>
       </c>
@@ -27824,7 +27837,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="415" spans="1:17">
+    <row r="415" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A415" s="1" t="s">
         <v>1387</v>
       </c>
@@ -27877,7 +27890,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="416" spans="1:17">
+    <row r="416" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A416" s="1" t="s">
         <v>1391</v>
       </c>
@@ -27930,7 +27943,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="417" spans="1:17">
+    <row r="417" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A417" s="1" t="s">
         <v>108</v>
       </c>
@@ -27983,7 +27996,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="418" spans="1:17">
+    <row r="418" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A418" s="1" t="s">
         <v>1139</v>
       </c>
@@ -28036,7 +28049,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="419" spans="1:17">
+    <row r="419" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A419" s="1" t="s">
         <v>1396</v>
       </c>
@@ -28089,7 +28102,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="420" spans="1:17">
+    <row r="420" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A420" s="1" t="s">
         <v>1402</v>
       </c>
@@ -28142,7 +28155,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="421" spans="1:17">
+    <row r="421" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A421" s="1" t="s">
         <v>1405</v>
       </c>
@@ -28195,7 +28208,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="422" spans="1:17">
+    <row r="422" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A422" s="1" t="s">
         <v>1408</v>
       </c>
@@ -28248,7 +28261,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="423" spans="1:17">
+    <row r="423" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A423" s="1" t="s">
         <v>1091</v>
       </c>
@@ -28301,7 +28314,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="424" spans="1:17">
+    <row r="424" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A424" s="1" t="s">
         <v>1411</v>
       </c>
@@ -28354,7 +28367,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="425" spans="1:17">
+    <row r="425" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A425" s="1" t="s">
         <v>1413</v>
       </c>
@@ -28407,7 +28420,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="426" spans="1:17">
+    <row r="426" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A426" s="1" t="s">
         <v>162</v>
       </c>
@@ -28460,7 +28473,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="427" spans="1:17">
+    <row r="427" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A427" s="1" t="s">
         <v>1420</v>
       </c>
@@ -28513,7 +28526,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="428" spans="1:17">
+    <row r="428" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A428" s="1" t="s">
         <v>1423</v>
       </c>
@@ -28566,7 +28579,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="429" spans="1:17">
+    <row r="429" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A429" s="1" t="s">
         <v>1232</v>
       </c>
@@ -28619,7 +28632,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="430" spans="1:17">
+    <row r="430" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A430" s="1" t="s">
         <v>1426</v>
       </c>
@@ -28672,7 +28685,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="431" spans="1:17">
+    <row r="431" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A431" s="1" t="s">
         <v>1429</v>
       </c>
@@ -28725,7 +28738,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="432" spans="1:17">
+    <row r="432" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A432" s="1" t="s">
         <v>1434</v>
       </c>
@@ -28778,7 +28791,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="433" spans="1:17">
+    <row r="433" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A433" s="1" t="s">
         <v>1437</v>
       </c>
@@ -28831,7 +28844,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="434" spans="1:17">
+    <row r="434" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A434" s="1" t="s">
         <v>80</v>
       </c>
@@ -28884,7 +28897,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="435" spans="1:17">
+    <row r="435" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A435" s="1" t="s">
         <v>842</v>
       </c>
@@ -28937,7 +28950,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="436" spans="1:17">
+    <row r="436" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A436" s="1" t="s">
         <v>1440</v>
       </c>
@@ -28990,7 +29003,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="437" spans="1:17">
+    <row r="437" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A437" s="1" t="s">
         <v>304</v>
       </c>
@@ -29043,7 +29056,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="438" spans="1:17">
+    <row r="438" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A438" s="1" t="s">
         <v>300</v>
       </c>
@@ -29096,7 +29109,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="439" spans="1:17">
+    <row r="439" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A439" s="1" t="s">
         <v>606</v>
       </c>
@@ -29149,7 +29162,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="440" spans="1:17">
+    <row r="440" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A440" s="1" t="s">
         <v>1446</v>
       </c>
@@ -29202,7 +29215,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="441" spans="1:17">
+    <row r="441" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A441" s="1" t="s">
         <v>1449</v>
       </c>
@@ -29255,7 +29268,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="442" spans="1:17">
+    <row r="442" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A442" s="1" t="s">
         <v>457</v>
       </c>
@@ -29308,7 +29321,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="443" spans="1:17">
+    <row r="443" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A443" s="1" t="s">
         <v>1452</v>
       </c>
@@ -29361,7 +29374,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="444" spans="1:17">
+    <row r="444" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A444" s="1" t="s">
         <v>1458</v>
       </c>
@@ -29414,7 +29427,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="445" spans="1:17">
+    <row r="445" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A445" s="1" t="s">
         <v>1461</v>
       </c>
@@ -29467,7 +29480,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="446" spans="1:17">
+    <row r="446" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A446" s="1" t="s">
         <v>180</v>
       </c>
@@ -29520,7 +29533,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="447" spans="1:17">
+    <row r="447" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A447" s="1" t="s">
         <v>1384</v>
       </c>
@@ -29573,7 +29586,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="448" spans="1:17">
+    <row r="448" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A448" s="1" t="s">
         <v>1465</v>
       </c>
@@ -29626,7 +29639,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="449" spans="1:17">
+    <row r="449" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A449" s="1" t="s">
         <v>674</v>
       </c>
@@ -29679,7 +29692,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="450" spans="1:17">
+    <row r="450" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A450" s="1" t="s">
         <v>72</v>
       </c>
@@ -29732,7 +29745,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="451" spans="1:17">
+    <row r="451" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A451" s="1" t="s">
         <v>33</v>
       </c>
@@ -29785,7 +29798,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="452" spans="1:17">
+    <row r="452" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A452" s="1" t="s">
         <v>1139</v>
       </c>
@@ -29838,7 +29851,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="453" spans="1:17">
+    <row r="453" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A453" s="1" t="s">
         <v>793</v>
       </c>
@@ -29891,7 +29904,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="454" spans="1:17">
+    <row r="454" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A454" s="1" t="s">
         <v>1472</v>
       </c>
@@ -29944,7 +29957,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="455" spans="1:17">
+    <row r="455" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A455" s="1" t="s">
         <v>1476</v>
       </c>
@@ -29997,7 +30010,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="456" spans="1:17">
+    <row r="456" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A456" s="1" t="s">
         <v>1482</v>
       </c>
@@ -30050,7 +30063,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="457" spans="1:17">
+    <row r="457" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A457" s="1" t="s">
         <v>1262</v>
       </c>
@@ -30103,7 +30116,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="458" spans="1:17">
+    <row r="458" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A458" s="1" t="s">
         <v>494</v>
       </c>
@@ -30156,7 +30169,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="459" spans="1:17">
+    <row r="459" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A459" s="1" t="s">
         <v>872</v>
       </c>
@@ -30209,7 +30222,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="460" spans="1:17">
+    <row r="460" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A460" s="1" t="s">
         <v>1485</v>
       </c>
@@ -30262,7 +30275,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="461" spans="1:17">
+    <row r="461" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A461" s="1" t="s">
         <v>1104</v>
       </c>
@@ -30315,7 +30328,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="462" spans="1:17">
+    <row r="462" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A462" s="1" t="s">
         <v>330</v>
       </c>
@@ -30368,7 +30381,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="463" spans="1:17">
+    <row r="463" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A463" s="1" t="s">
         <v>934</v>
       </c>
@@ -30421,7 +30434,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="464" spans="1:17">
+    <row r="464" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A464" s="1" t="s">
         <v>1494</v>
       </c>
@@ -30474,7 +30487,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="465" spans="1:17">
+    <row r="465" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A465" s="1" t="s">
         <v>1497</v>
       </c>
@@ -30527,7 +30540,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="466" spans="1:17">
+    <row r="466" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A466" s="1" t="s">
         <v>880</v>
       </c>
@@ -30580,7 +30593,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="467" spans="1:17">
+    <row r="467" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A467" s="1" t="s">
         <v>868</v>
       </c>
@@ -30633,7 +30646,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="468" spans="1:17">
+    <row r="468" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A468" s="1" t="s">
         <v>1503</v>
       </c>
@@ -30686,7 +30699,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="469" spans="1:17">
+    <row r="469" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A469" s="1" t="s">
         <v>1506</v>
       </c>
@@ -30739,7 +30752,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="470" spans="1:17">
+    <row r="470" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A470" s="1" t="s">
         <v>828</v>
       </c>
@@ -30792,7 +30805,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="471" spans="1:17">
+    <row r="471" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A471" s="1" t="s">
         <v>479</v>
       </c>
@@ -30845,7 +30858,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="472" spans="1:17">
+    <row r="472" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A472" s="1" t="s">
         <v>1429</v>
       </c>
@@ -30898,7 +30911,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="473" spans="1:17">
+    <row r="473" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A473" s="1" t="s">
         <v>380</v>
       </c>
@@ -30951,7 +30964,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="474" spans="1:17">
+    <row r="474" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A474" s="1" t="s">
         <v>89</v>
       </c>
@@ -31004,7 +31017,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="475" spans="1:17">
+    <row r="475" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A475" s="1" t="s">
         <v>135</v>
       </c>
@@ -31057,7 +31070,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="476" spans="1:17">
+    <row r="476" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A476" s="1" t="s">
         <v>1408</v>
       </c>
@@ -31110,7 +31123,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="477" spans="1:17">
+    <row r="477" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A477" s="1" t="s">
         <v>1513</v>
       </c>
@@ -31163,7 +31176,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="478" spans="1:17">
+    <row r="478" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A478" s="1" t="s">
         <v>146</v>
       </c>
@@ -31216,7 +31229,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="479" spans="1:17">
+    <row r="479" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A479" s="1" t="s">
         <v>323</v>
       </c>
@@ -31269,7 +31282,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="480" spans="1:17">
+    <row r="480" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A480" s="1" t="s">
         <v>296</v>
       </c>
@@ -31322,7 +31335,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="481" spans="1:17">
+    <row r="481" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A481" s="1" t="s">
         <v>278</v>
       </c>
@@ -31375,7 +31388,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="482" spans="1:17">
+    <row r="482" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A482" s="1" t="s">
         <v>1521</v>
       </c>
@@ -31428,7 +31441,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="483" spans="1:17">
+    <row r="483" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A483" s="1" t="s">
         <v>1525</v>
       </c>
@@ -31481,7 +31494,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="484" spans="1:17">
+    <row r="484" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A484" s="1" t="s">
         <v>917</v>
       </c>
@@ -31534,7 +31547,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="485" spans="1:17">
+    <row r="485" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A485" s="1" t="s">
         <v>1528</v>
       </c>
@@ -31587,7 +31600,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="486" spans="1:17">
+    <row r="486" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A486" s="1" t="s">
         <v>1532</v>
       </c>
@@ -31640,7 +31653,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="487" spans="1:17">
+    <row r="487" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A487" s="1" t="s">
         <v>176</v>
       </c>
@@ -31693,7 +31706,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="488" spans="1:17">
+    <row r="488" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A488" s="1" t="s">
         <v>464</v>
       </c>
@@ -31746,7 +31759,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="489" spans="1:17">
+    <row r="489" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A489" s="1" t="s">
         <v>1539</v>
       </c>
@@ -31799,7 +31812,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="490" spans="1:17">
+    <row r="490" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A490" s="1" t="s">
         <v>1543</v>
       </c>
@@ -31852,7 +31865,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="491" spans="1:17">
+    <row r="491" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A491" s="1" t="s">
         <v>1546</v>
       </c>
@@ -31905,7 +31918,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="492" spans="1:17">
+    <row r="492" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A492" s="1" t="s">
         <v>1246</v>
       </c>
@@ -31958,7 +31971,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="493" spans="1:17">
+    <row r="493" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A493" s="1" t="s">
         <v>41</v>
       </c>
@@ -32011,7 +32024,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="494" spans="1:17">
+    <row r="494" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A494" s="1" t="s">
         <v>654</v>
       </c>
@@ -32064,7 +32077,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="495" spans="1:17">
+    <row r="495" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A495" s="1" t="s">
         <v>330</v>
       </c>
@@ -32117,7 +32130,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="496" spans="1:17">
+    <row r="496" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A496" s="1" t="s">
         <v>1337</v>
       </c>
@@ -32170,7 +32183,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="497" spans="1:17">
+    <row r="497" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A497" s="1" t="s">
         <v>146</v>
       </c>
@@ -32223,7 +32236,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="498" spans="1:17">
+    <row r="498" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A498" s="1" t="s">
         <v>1557</v>
       </c>
@@ -32276,7 +32289,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="499" spans="1:17">
+    <row r="499" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A499" s="1" t="s">
         <v>1562</v>
       </c>
@@ -32329,7 +32342,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="500" spans="1:17">
+    <row r="500" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A500" s="1" t="s">
         <v>1566</v>
       </c>
@@ -32382,7 +32395,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="501" spans="1:17">
+    <row r="501" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A501" s="1" t="s">
         <v>1570</v>
       </c>
@@ -32435,7 +32448,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="502" spans="1:17">
+    <row r="502" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A502" s="1" t="s">
         <v>1573</v>
       </c>
@@ -32488,7 +32501,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="503" spans="1:17">
+    <row r="503" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A503" s="1" t="s">
         <v>1576</v>
       </c>
@@ -32541,7 +32554,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="504" spans="1:17">
+    <row r="504" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A504" s="1" t="s">
         <v>323</v>
       </c>
@@ -32594,7 +32607,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="505" spans="1:17">
+    <row r="505" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A505" s="1" t="s">
         <v>1587</v>
       </c>
@@ -32647,7 +32660,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="506" spans="1:17">
+    <row r="506" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A506" s="1" t="s">
         <v>880</v>
       </c>
@@ -32700,7 +32713,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="507" spans="1:17">
+    <row r="507" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A507" s="1" t="s">
         <v>1591</v>
       </c>
@@ -32753,7 +32766,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="508" spans="1:17">
+    <row r="508" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A508" s="1" t="s">
         <v>846</v>
       </c>
@@ -32806,7 +32819,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="509" spans="1:17">
+    <row r="509" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A509" s="1" t="s">
         <v>1595</v>
       </c>
@@ -32859,7 +32872,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="510" spans="1:17">
+    <row r="510" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A510" s="1" t="s">
         <v>1532</v>
       </c>
@@ -32912,7 +32925,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="511" spans="1:17">
+    <row r="511" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A511" s="1" t="s">
         <v>1599</v>
       </c>
@@ -32965,7 +32978,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="512" spans="1:17">
+    <row r="512" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A512" s="1" t="s">
         <v>1603</v>
       </c>
@@ -33018,7 +33031,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="513" spans="1:17">
+    <row r="513" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A513" s="1" t="s">
         <v>1055</v>
       </c>
@@ -33071,7 +33084,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="514" spans="1:17">
+    <row r="514" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A514" s="1" t="s">
         <v>497</v>
       </c>
@@ -33124,7 +33137,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="515" spans="1:17">
+    <row r="515" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A515" s="1" t="s">
         <v>1217</v>
       </c>
@@ -33177,7 +33190,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="516" spans="1:17">
+    <row r="516" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A516" s="1" t="s">
         <v>127</v>
       </c>
@@ -33230,7 +33243,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="517" spans="1:17">
+    <row r="517" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A517" s="1" t="s">
         <v>872</v>
       </c>
@@ -33283,7 +33296,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="518" spans="1:17">
+    <row r="518" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A518" s="1" t="s">
         <v>1091</v>
       </c>
@@ -33336,7 +33349,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="519" spans="1:17">
+    <row r="519" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A519" s="1" t="s">
         <v>1609</v>
       </c>
@@ -33389,7 +33402,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="520" spans="1:17">
+    <row r="520" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A520" s="1" t="s">
         <v>1573</v>
       </c>
@@ -33442,7 +33455,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="521" spans="1:17">
+    <row r="521" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A521" s="1" t="s">
         <v>304</v>
       </c>
@@ -33495,7 +33508,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="522" spans="1:17">
+    <row r="522" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A522" s="1" t="s">
         <v>300</v>
       </c>
@@ -33548,7 +33561,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="523" spans="1:17">
+    <row r="523" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A523" s="1" t="s">
         <v>274</v>
       </c>
@@ -33601,7 +33614,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="524" spans="1:17">
+    <row r="524" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A524" s="1" t="s">
         <v>1616</v>
       </c>
@@ -33654,7 +33667,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="525" spans="1:17">
+    <row r="525" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A525" s="1" t="s">
         <v>1620</v>
       </c>
@@ -33707,7 +33720,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="526" spans="1:17">
+    <row r="526" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A526" s="1" t="s">
         <v>1625</v>
       </c>
@@ -33760,7 +33773,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="527" spans="1:17">
+    <row r="527" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A527" s="1" t="s">
         <v>1528</v>
       </c>
@@ -33813,7 +33826,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="528" spans="1:17">
+    <row r="528" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A528" s="1" t="s">
         <v>1566</v>
       </c>
@@ -33866,7 +33879,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="529" spans="1:17">
+    <row r="529" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A529" s="1" t="s">
         <v>348</v>
       </c>
@@ -33919,7 +33932,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="530" spans="1:17">
+    <row r="530" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A530" s="1" t="s">
         <v>558</v>
       </c>
@@ -33972,7 +33985,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="531" spans="1:17">
+    <row r="531" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A531" s="1" t="s">
         <v>1039</v>
       </c>
@@ -34025,7 +34038,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="532" spans="1:17">
+    <row r="532" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A532" s="1" t="s">
         <v>1631</v>
       </c>
@@ -34078,7 +34091,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="533" spans="1:17">
+    <row r="533" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A533" s="1" t="s">
         <v>1634</v>
       </c>
@@ -34131,7 +34144,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="534" spans="1:17">
+    <row r="534" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A534" s="1" t="s">
         <v>960</v>
       </c>
@@ -34184,7 +34197,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="535" spans="1:17">
+    <row r="535" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A535" s="1" t="s">
         <v>1641</v>
       </c>
@@ -34237,7 +34250,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="536" spans="1:17">
+    <row r="536" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A536" s="1" t="s">
         <v>1644</v>
       </c>
@@ -34290,7 +34303,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="537" spans="1:17">
+    <row r="537" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A537" s="1" t="s">
         <v>1648</v>
       </c>
@@ -34343,7 +34356,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="538" spans="1:17">
+    <row r="538" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A538" s="1" t="s">
         <v>908</v>
       </c>
@@ -34396,7 +34409,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="539" spans="1:17">
+    <row r="539" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A539" s="1" t="s">
         <v>1652</v>
       </c>
@@ -34449,7 +34462,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="540" spans="1:17">
+    <row r="540" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A540" s="1" t="s">
         <v>1658</v>
       </c>
@@ -34502,7 +34515,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="541" spans="1:17">
+    <row r="541" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A541" s="1" t="s">
         <v>260</v>
       </c>
@@ -34555,7 +34568,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="542" spans="1:17">
+    <row r="542" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A542" s="1" t="s">
         <v>1661</v>
       </c>
@@ -34608,7 +34621,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="543" spans="1:17">
+    <row r="543" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A543" s="1" t="s">
         <v>1217</v>
       </c>
@@ -34661,7 +34674,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="544" spans="1:17">
+    <row r="544" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A544" s="1" t="s">
         <v>1521</v>
       </c>
@@ -34714,7 +34727,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="545" spans="1:17">
+    <row r="545" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A545" s="1" t="s">
         <v>1525</v>
       </c>
@@ -34767,7 +34780,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="546" spans="1:17">
+    <row r="546" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A546" s="1" t="s">
         <v>1666</v>
       </c>
@@ -34820,7 +34833,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="547" spans="1:17">
+    <row r="547" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A547" s="1" t="s">
         <v>1449</v>
       </c>
@@ -34873,7 +34886,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="548" spans="1:17">
+    <row r="548" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A548" s="1" t="s">
         <v>1669</v>
       </c>
@@ -34926,7 +34939,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="549" spans="1:17">
+    <row r="549" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A549" s="1" t="s">
         <v>1420</v>
       </c>
@@ -34979,7 +34992,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="550" spans="1:17">
+    <row r="550" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A550" s="1" t="s">
         <v>1437</v>
       </c>
@@ -35032,7 +35045,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="551" spans="1:17">
+    <row r="551" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A551" s="1" t="s">
         <v>1676</v>
       </c>
@@ -35085,7 +35098,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="552" spans="1:17">
+    <row r="552" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A552" s="1" t="s">
         <v>561</v>
       </c>
@@ -35138,7 +35151,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="553" spans="1:17">
+    <row r="553" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A553" s="1" t="s">
         <v>278</v>
       </c>
@@ -35191,7 +35204,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="554" spans="1:17">
+    <row r="554" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A554" s="1" t="s">
         <v>300</v>
       </c>
@@ -35244,7 +35257,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="555" spans="1:17">
+    <row r="555" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A555" s="1" t="s">
         <v>304</v>
       </c>
@@ -35297,7 +35310,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="556" spans="1:17">
+    <row r="556" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A556" s="1" t="s">
         <v>1246</v>
       </c>
@@ -35350,7 +35363,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="557" spans="1:17">
+    <row r="557" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A557" s="1" t="s">
         <v>398</v>
       </c>
@@ -35403,7 +35416,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="558" spans="1:17">
+    <row r="558" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A558" s="1" t="s">
         <v>1681</v>
       </c>
@@ -35456,7 +35469,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="559" spans="1:17">
+    <row r="559" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A559" s="1" t="s">
         <v>1685</v>
       </c>
@@ -35509,7 +35522,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="560" spans="1:17">
+    <row r="560" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A560" s="1" t="s">
         <v>583</v>
       </c>
@@ -35562,7 +35575,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="561" spans="1:17">
+    <row r="561" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A561" s="1" t="s">
         <v>1691</v>
       </c>
@@ -35615,7 +35628,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="562" spans="1:17">
+    <row r="562" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A562" s="1" t="s">
         <v>1695</v>
       </c>
@@ -35668,7 +35681,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="563" spans="1:17">
+    <row r="563" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A563" s="1" t="s">
         <v>951</v>
       </c>
@@ -35721,7 +35734,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="564" spans="1:17">
+    <row r="564" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A564" s="1" t="s">
         <v>1698</v>
       </c>
@@ -35774,7 +35787,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="565" spans="1:17">
+    <row r="565" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A565" s="1" t="s">
         <v>1701</v>
       </c>
@@ -35827,7 +35840,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="566" spans="1:17">
+    <row r="566" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A566" s="1" t="s">
         <v>1705</v>
       </c>
@@ -35880,7 +35893,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="567" spans="1:17">
+    <row r="567" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A567" s="1" t="s">
         <v>383</v>
       </c>
@@ -35933,7 +35946,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="568" spans="1:17">
+    <row r="568" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A568" s="1" t="s">
         <v>1710</v>
       </c>
@@ -35986,7 +35999,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="569" spans="1:17">
+    <row r="569" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A569" s="1" t="s">
         <v>1543</v>
       </c>
@@ -36039,7 +36052,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="570" spans="1:17">
+    <row r="570" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A570" s="1" t="s">
         <v>828</v>
       </c>
@@ -36092,7 +36105,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="571" spans="1:17">
+    <row r="571" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A571" s="1" t="s">
         <v>1232</v>
       </c>
@@ -36145,7 +36158,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="572" spans="1:17">
+    <row r="572" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A572" s="1" t="s">
         <v>1714</v>
       </c>
@@ -36198,7 +36211,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="573" spans="1:17">
+    <row r="573" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A573" s="1" t="s">
         <v>1719</v>
       </c>
@@ -36251,7 +36264,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="574" spans="1:17">
+    <row r="574" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A574" s="1" t="s">
         <v>963</v>
       </c>
@@ -36304,7 +36317,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="575" spans="1:17">
+    <row r="575" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A575" s="1" t="s">
         <v>1426</v>
       </c>
@@ -36357,7 +36370,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="576" spans="1:17">
+    <row r="576" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A576" s="1" t="s">
         <v>1722</v>
       </c>
@@ -36410,7 +36423,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="577" spans="1:17">
+    <row r="577" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A577" s="1" t="s">
         <v>1726</v>
       </c>
@@ -36463,7 +36476,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="578" spans="1:17">
+    <row r="578" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A578" s="1" t="s">
         <v>1730</v>
       </c>
@@ -36516,7 +36529,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="579" spans="1:17">
+    <row r="579" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A579" s="1" t="s">
         <v>115</v>
       </c>
@@ -36569,7 +36582,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="580" spans="1:17">
+    <row r="580" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A580" s="1" t="s">
         <v>1736</v>
       </c>
@@ -36622,7 +36635,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="581" spans="1:17">
+    <row r="581" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A581" s="1" t="s">
         <v>1387</v>
       </c>
@@ -36675,7 +36688,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="582" spans="1:17">
+    <row r="582" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A582" s="1" t="s">
         <v>884</v>
       </c>
@@ -36728,7 +36741,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="583" spans="1:17">
+    <row r="583" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A583" s="1" t="s">
         <v>852</v>
       </c>
@@ -36781,7 +36794,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="584" spans="1:17">
+    <row r="584" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A584" s="1" t="s">
         <v>1738</v>
       </c>
@@ -36834,7 +36847,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="585" spans="1:17">
+    <row r="585" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A585" s="1" t="s">
         <v>1744</v>
       </c>
@@ -36887,7 +36900,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="586" spans="1:17">
+    <row r="586" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A586" s="1" t="s">
         <v>1747</v>
       </c>
@@ -36940,7 +36953,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="587" spans="1:17">
+    <row r="587" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A587" s="1" t="s">
         <v>1750</v>
       </c>
@@ -36993,7 +37006,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="588" spans="1:17">
+    <row r="588" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A588" s="1" t="s">
         <v>1753</v>
       </c>
@@ -37046,7 +37059,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="589" spans="1:17">
+    <row r="589" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A589" s="1" t="s">
         <v>1756</v>
       </c>
@@ -37099,7 +37112,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="590" spans="1:17">
+    <row r="590" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A590" s="1" t="s">
         <v>1759</v>
       </c>
@@ -37152,7 +37165,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="591" spans="1:17">
+    <row r="591" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A591" s="1" t="s">
         <v>1525</v>
       </c>
@@ -37205,7 +37218,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="592" spans="1:17">
+    <row r="592" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A592" s="1" t="s">
         <v>1766</v>
       </c>
@@ -37258,7 +37271,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="593" spans="1:17">
+    <row r="593" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A593" s="1" t="s">
         <v>684</v>
       </c>
@@ -37311,7 +37324,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="594" spans="1:17">
+    <row r="594" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A594" s="1" t="s">
         <v>1595</v>
       </c>
@@ -37364,7 +37377,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="595" spans="1:17">
+    <row r="595" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A595" s="1" t="s">
         <v>1770</v>
       </c>
@@ -37417,7 +37430,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="596" spans="1:17">
+    <row r="596" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A596" s="1" t="s">
         <v>996</v>
       </c>
@@ -37470,7 +37483,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="597" spans="1:17">
+    <row r="597" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A597" s="1" t="s">
         <v>1776</v>
       </c>
@@ -37523,7 +37536,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="598" spans="1:17">
+    <row r="598" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A598" s="1" t="s">
         <v>1780</v>
       </c>
@@ -37576,7 +37589,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="599" spans="1:17">
+    <row r="599" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A599" s="1" t="s">
         <v>1485</v>
       </c>
@@ -37629,7 +37642,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="600" spans="1:17">
+    <row r="600" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A600" s="1" t="s">
         <v>1783</v>
       </c>
@@ -37682,7 +37695,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="601" spans="1:17">
+    <row r="601" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A601" s="1" t="s">
         <v>1786</v>
       </c>
@@ -37735,7 +37748,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="602" spans="1:17">
+    <row r="602" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A602" s="1" t="s">
         <v>1790</v>
       </c>
@@ -37788,7 +37801,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="603" spans="1:17">
+    <row r="603" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A603" s="1" t="s">
         <v>1795</v>
       </c>
@@ -37841,7 +37854,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="604" spans="1:17">
+    <row r="604" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A604" s="1" t="s">
         <v>1798</v>
       </c>
@@ -37894,7 +37907,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="605" spans="1:17">
+    <row r="605" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A605" s="1" t="s">
         <v>1801</v>
       </c>
@@ -37947,7 +37960,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="606" spans="1:17">
+    <row r="606" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A606" s="1" t="s">
         <v>1804</v>
       </c>
@@ -38000,7 +38013,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="607" spans="1:17">
+    <row r="607" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A607" s="1" t="s">
         <v>1807</v>
       </c>
@@ -38053,7 +38066,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="608" spans="1:17">
+    <row r="608" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A608" s="1" t="s">
         <v>457</v>
       </c>
@@ -38106,7 +38119,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="609" spans="1:17">
+    <row r="609" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A609" s="1" t="s">
         <v>1813</v>
       </c>
@@ -38159,7 +38172,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="610" spans="1:17">
+    <row r="610" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A610" s="1" t="s">
         <v>1411</v>
       </c>
@@ -38212,7 +38225,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="611" spans="1:17">
+    <row r="611" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A611" s="1" t="s">
         <v>739</v>
       </c>
@@ -38265,7 +38278,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="612" spans="1:17">
+    <row r="612" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A612" s="1" t="s">
         <v>1816</v>
       </c>
@@ -38318,7 +38331,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="613" spans="1:17">
+    <row r="613" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A613" s="1" t="s">
         <v>1147</v>
       </c>
@@ -38371,7 +38384,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="614" spans="1:17">
+    <row r="614" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A614" s="1" t="s">
         <v>1710</v>
       </c>
@@ -38424,7 +38437,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="615" spans="1:17">
+    <row r="615" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A615" s="1" t="s">
         <v>1821</v>
       </c>
@@ -38477,7 +38490,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="616" spans="1:17">
+    <row r="616" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A616" s="1" t="s">
         <v>176</v>
       </c>
@@ -38530,7 +38543,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="617" spans="1:17">
+    <row r="617" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A617" s="1" t="s">
         <v>1824</v>
       </c>
@@ -38583,7 +38596,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="618" spans="1:17">
+    <row r="618" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A618" s="1" t="s">
         <v>1827</v>
       </c>
@@ -38636,7 +38649,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="619" spans="1:17">
+    <row r="619" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A619" s="1" t="s">
         <v>1830</v>
       </c>
@@ -38689,7 +38702,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="620" spans="1:17">
+    <row r="620" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A620" s="1" t="s">
         <v>1420</v>
       </c>
@@ -38742,7 +38755,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="621" spans="1:17">
+    <row r="621" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A621" s="1" t="s">
         <v>1669</v>
       </c>
@@ -38795,7 +38808,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="622" spans="1:17">
+    <row r="622" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A622" s="1" t="s">
         <v>207</v>
       </c>
@@ -38848,7 +38861,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="623" spans="1:17">
+    <row r="623" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A623" s="1" t="s">
         <v>1836</v>
       </c>
@@ -38901,7 +38914,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="624" spans="1:17">
+    <row r="624" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A624" s="1" t="s">
         <v>1839</v>
       </c>
@@ -38955,18 +38968,10 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
-  <printOptions gridLines="false" gridLinesSet="true"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
+  <headerFooter>
+    <oddFooter>&amp;R_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Information classification: Internal</oddFooter>
   </headerFooter>
-  <tableParts count="0"/>
 </worksheet>
 </file>